--- a/Apostas_Diarias/Apostas_20260419.xlsx
+++ b/Apostas_Diarias/Apostas_20260419.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_28918C429526CB11C123DCF0505ED87656CDA656" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C6F4382-9370-4715-93EF-2F8AE38B4D7E}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_2B590F4F95364D6A7D82DFF05075E070487BE3A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7370DC1-C412-461B-A562-9F5BBE70D171}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -74,13 +74,13 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>08:30:00</t>
-  </si>
-  <si>
-    <t>TURKEY 1</t>
-  </si>
-  <si>
-    <t>Kasimpasa x Alanyaspor</t>
+    <t>07:30:00</t>
+  </si>
+  <si>
+    <t>ITALY 1</t>
+  </si>
+  <si>
+    <t>US Cremonese x Torino</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
@@ -95,51 +95,6 @@
     <t>Paide Linnameeskond x Nomme Kalju</t>
   </si>
   <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
-    <t>NORWAY 2</t>
-  </si>
-  <si>
-    <t>Asane x Strommen</t>
-  </si>
-  <si>
-    <t>Egersund x Bryne</t>
-  </si>
-  <si>
-    <t>NORWAY 1</t>
-  </si>
-  <si>
-    <t>Ham-Kam x KFUM Oslo</t>
-  </si>
-  <si>
-    <t>Sarpsborg x Tromso</t>
-  </si>
-  <si>
-    <t>12:15:00</t>
-  </si>
-  <si>
-    <t>ROMANIA 1</t>
-  </si>
-  <si>
-    <t>ACS Petrolul 52 x Hermannstadt</t>
-  </si>
-  <si>
-    <t>FRANCE 1</t>
-  </si>
-  <si>
-    <t>Nantes x Brest</t>
-  </si>
-  <si>
-    <t>12:30:00</t>
-  </si>
-  <si>
-    <t>POLAND 1</t>
-  </si>
-  <si>
-    <t>Arka Gdynia x Jagiellonia Bialystock</t>
-  </si>
-  <si>
     <t>13:00:00</t>
   </si>
   <si>
@@ -158,31 +113,16 @@
     <t>Albacete x Granada</t>
   </si>
   <si>
-    <t>14:15:00</t>
-  </si>
-  <si>
-    <t>Start x Molde</t>
-  </si>
-  <si>
     <t>P2</t>
   </si>
   <si>
-    <t>10:30:00</t>
-  </si>
-  <si>
-    <t>CZECH 1</t>
-  </si>
-  <si>
-    <t>Hradec Kralove x Slavia Prague</t>
-  </si>
-  <si>
-    <t>P3</t>
+    <t>Pisa x Genoa</t>
+  </si>
+  <si>
+    <t>P4</t>
   </si>
   <si>
     <t>Lay_CS_1x0_B365</t>
-  </si>
-  <si>
-    <t>P4</t>
   </si>
 </sst>
 </file>
@@ -522,14 +462,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="5" max="5" width="37" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -581,22 +521,22 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="H2">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>500</v>
@@ -607,7 +547,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>44.523809523809526</v>
+        <v>58.4375</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -618,36 +558,36 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="I3">
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J20" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J9" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K20" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>75.403225806451616</v>
+        <f t="shared" ref="K3:K9" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>42.5</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -661,22 +601,22 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="H4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I4">
         <v>500</v>
@@ -687,7 +627,7 @@
       </c>
       <c r="K4">
         <f t="shared" si="1"/>
-        <v>46.75</v>
+        <v>44.523809523809526</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -698,25 +638,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>9.1999999999999993</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>9.1999999999999993</v>
+        <v>11</v>
       </c>
       <c r="I5">
         <v>500</v>
@@ -727,7 +667,7 @@
       </c>
       <c r="K5">
         <f t="shared" si="1"/>
-        <v>57.01219512195123</v>
+        <v>46.75</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -738,25 +678,25 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6">
-        <v>10.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H6">
-        <v>10.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I6">
         <v>500</v>
@@ -767,7 +707,7 @@
       </c>
       <c r="K6">
         <f t="shared" si="1"/>
-        <v>49.210526315789473</v>
+        <v>64.930555555555557</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -778,25 +718,25 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="H7">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="I7">
         <v>500</v>
@@ -807,7 +747,7 @@
       </c>
       <c r="K7">
         <f t="shared" si="1"/>
-        <v>37.400000000000006</v>
+        <v>49.210526315789473</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -818,25 +758,25 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>500</v>
@@ -847,7 +787,7 @@
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>38.958333333333336</v>
+        <v>58.4375</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -858,25 +798,25 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G9">
-        <v>16</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H9">
-        <v>16</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="I9">
         <v>500</v>
@@ -887,456 +827,13 @@
       </c>
       <c r="K9">
         <f t="shared" si="1"/>
-        <v>31.166666666666668</v>
+        <v>57.01219512195123</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10">
-        <v>12.5</v>
-      </c>
-      <c r="H10">
-        <v>12.5</v>
-      </c>
-      <c r="I10">
-        <v>500</v>
-      </c>
-      <c r="J10" t="str">
-        <f t="shared" si="0"/>
-        <v>RED</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="1"/>
-        <v>-500</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11">
-        <v>11.5</v>
-      </c>
-      <c r="H11">
-        <v>11.5</v>
-      </c>
-      <c r="I11">
-        <v>500</v>
-      </c>
-      <c r="J11" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="1"/>
-        <v>44.523809523809526</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="H12">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="I12">
-        <v>500</v>
-      </c>
-      <c r="J12" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="1"/>
-        <v>59.935897435897431</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13">
-        <v>11</v>
-      </c>
-      <c r="H13">
-        <v>11</v>
-      </c>
-      <c r="I13">
-        <v>500</v>
-      </c>
-      <c r="J13" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="1"/>
-        <v>46.75</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14">
-        <v>10.5</v>
-      </c>
-      <c r="H14">
-        <v>10.5</v>
-      </c>
-      <c r="I14">
-        <v>500</v>
-      </c>
-      <c r="J14" t="str">
-        <f t="shared" si="0"/>
-        <v>RED</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="1"/>
-        <v>-500</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15">
-        <v>10.5</v>
-      </c>
-      <c r="H15">
-        <v>10.5</v>
-      </c>
-      <c r="I15">
-        <v>500</v>
-      </c>
-      <c r="J15" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>49.210526315789473</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="H16">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="I16">
-        <v>500</v>
-      </c>
-      <c r="J16" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>59.935897435897431</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17">
-        <v>12</v>
-      </c>
-      <c r="H17">
-        <v>12</v>
-      </c>
-      <c r="I17">
-        <v>500</v>
-      </c>
-      <c r="J17" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>42.5</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18">
-        <v>11.5</v>
-      </c>
-      <c r="H18">
-        <v>11.5</v>
-      </c>
-      <c r="I18">
-        <v>500</v>
-      </c>
-      <c r="J18" t="str">
-        <f t="shared" si="0"/>
-        <v>RED</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>-500</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19">
-        <v>12</v>
-      </c>
-      <c r="H19">
-        <v>12</v>
-      </c>
-      <c r="I19">
-        <v>500</v>
-      </c>
-      <c r="J19" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>42.5</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20">
-        <v>11.5</v>
-      </c>
-      <c r="H20">
-        <v>11.5</v>
-      </c>
-      <c r="I20">
-        <v>500</v>
-      </c>
-      <c r="J20" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>44.523809523809526</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K20">
-    <sortCondition ref="E2:E20"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Apostas_Diarias/Apostas_20260419.xlsx
+++ b/Apostas_Diarias/Apostas_20260419.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_2B590F4F95364D6A7D82DFF05075E070487BE3A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7370DC1-C412-461B-A562-9F5BBE70D171}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_2B590F4F9506CB4CB1C2C0F050CC78B77359E152" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EA5875E-26D6-4A3B-BD8F-F265903F916B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="37">
   <si>
     <t>Data</t>
   </si>
@@ -86,13 +86,43 @@
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>11:00:00</t>
-  </si>
-  <si>
-    <t>ESTONIA 1</t>
-  </si>
-  <si>
-    <t>Paide Linnameeskond x Nomme Kalju</t>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>TURKEY 1</t>
+  </si>
+  <si>
+    <t>Kasimpasa x Alanyaspor</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>NORWAY 1</t>
+  </si>
+  <si>
+    <t>Ham-Kam x KFUM Oslo</t>
+  </si>
+  <si>
+    <t>Sarpsborg x Tromso</t>
+  </si>
+  <si>
+    <t>12:15:00</t>
+  </si>
+  <si>
+    <t>ROMANIA 1</t>
+  </si>
+  <si>
+    <t>ACS Petrolul 52 x Hermannstadt</t>
+  </si>
+  <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
+    <t>POLAND 1</t>
+  </si>
+  <si>
+    <t>Arka Gdynia x Jagiellonia Bialystock</t>
   </si>
   <si>
     <t>13:00:00</t>
@@ -102,15 +132,6 @@
   </si>
   <si>
     <t>Vejle x FC Copenhagen</t>
-  </si>
-  <si>
-    <t>13:30:00</t>
-  </si>
-  <si>
-    <t>SPAIN 2</t>
-  </si>
-  <si>
-    <t>Albacete x Granada</t>
   </si>
   <si>
     <t>P2</t>
@@ -462,14 +483,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="37" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -512,6 +533,9 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1">
+        <v>500</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -536,9 +560,11 @@
         <v>9</v>
       </c>
       <c r="H2">
+        <f>G2</f>
         <v>9</v>
       </c>
       <c r="I2">
+        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -573,21 +599,23 @@
         <v>16</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <f t="shared" ref="H3:H11" si="0">G3</f>
+        <v>11</v>
       </c>
       <c r="I3">
+        <f t="shared" ref="I3:I11" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J9" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J11" si="2">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K9" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>42.5</v>
+        <f t="shared" ref="K3:K11" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>46.75</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -616,17 +644,19 @@
         <v>11.5</v>
       </c>
       <c r="H4">
+        <f t="shared" si="0"/>
         <v>11.5</v>
       </c>
       <c r="I4">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>44.523809523809526</v>
       </c>
       <c r="L4">
@@ -641,36 +671,38 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
         <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="H5">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>11.5</v>
       </c>
       <c r="I5">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
+        <f t="shared" si="2"/>
+        <v>RED</v>
       </c>
       <c r="K5">
-        <f t="shared" si="1"/>
-        <v>46.75</v>
+        <f t="shared" si="3"/>
+        <v>-500</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -678,36 +710,38 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6">
-        <v>8.1999999999999993</v>
+        <v>11.5</v>
       </c>
       <c r="H6">
-        <v>8.1999999999999993</v>
+        <f t="shared" si="0"/>
+        <v>11.5</v>
       </c>
       <c r="I6">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K6">
-        <f t="shared" si="1"/>
-        <v>64.930555555555557</v>
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -718,35 +752,37 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G7">
         <v>10.5</v>
       </c>
       <c r="H7">
+        <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
       <c r="I7">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>49.210526315789473</v>
       </c>
       <c r="L7">
@@ -758,36 +794,38 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>11.5</v>
       </c>
       <c r="I8">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K8">
-        <f t="shared" si="1"/>
-        <v>58.4375</v>
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -798,38 +836,124 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G9">
-        <v>9.1999999999999993</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H9">
-        <v>9.1999999999999993</v>
+        <f t="shared" si="0"/>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I9">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J9" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>64.930555555555557</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10">
+        <v>10.5</v>
+      </c>
+      <c r="H10">
         <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
-      <c r="K9">
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11">
+        <v>9</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="I11">
         <f t="shared" si="1"/>
-        <v>57.01219512195123</v>
-      </c>
-      <c r="L9">
+        <v>500</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>58.4375</v>
+      </c>
+      <c r="L11">
         <v>1</v>
       </c>
     </row>

--- a/Apostas_Diarias/Apostas_20260419.xlsx
+++ b/Apostas_Diarias/Apostas_20260419.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_2B590F4F9506CB4CB1C2C0F050CC78B77359E152" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EA5875E-26D6-4A3B-BD8F-F265903F916B}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_2B590F4F95364D6A7D82DFF05075E070487BE3A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7370DC1-C412-461B-A562-9F5BBE70D171}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -86,43 +86,13 @@
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>08:30:00</t>
-  </si>
-  <si>
-    <t>TURKEY 1</t>
-  </si>
-  <si>
-    <t>Kasimpasa x Alanyaspor</t>
-  </si>
-  <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
-    <t>NORWAY 1</t>
-  </si>
-  <si>
-    <t>Ham-Kam x KFUM Oslo</t>
-  </si>
-  <si>
-    <t>Sarpsborg x Tromso</t>
-  </si>
-  <si>
-    <t>12:15:00</t>
-  </si>
-  <si>
-    <t>ROMANIA 1</t>
-  </si>
-  <si>
-    <t>ACS Petrolul 52 x Hermannstadt</t>
-  </si>
-  <si>
-    <t>12:30:00</t>
-  </si>
-  <si>
-    <t>POLAND 1</t>
-  </si>
-  <si>
-    <t>Arka Gdynia x Jagiellonia Bialystock</t>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>ESTONIA 1</t>
+  </si>
+  <si>
+    <t>Paide Linnameeskond x Nomme Kalju</t>
   </si>
   <si>
     <t>13:00:00</t>
@@ -132,6 +102,15 @@
   </si>
   <si>
     <t>Vejle x FC Copenhagen</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>SPAIN 2</t>
+  </si>
+  <si>
+    <t>Albacete x Granada</t>
   </si>
   <si>
     <t>P2</t>
@@ -483,14 +462,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="5" max="5" width="37" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -533,9 +512,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -560,11 +536,9 @@
         <v>9</v>
       </c>
       <c r="H2">
-        <f>G2</f>
         <v>9</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -599,23 +573,21 @@
         <v>16</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H11" si="0">G3</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I11" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J11" si="2">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J9" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K11" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>46.75</v>
+        <f t="shared" ref="K3:K9" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>42.5</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -644,19 +616,17 @@
         <v>11.5</v>
       </c>
       <c r="H4">
+        <v>11.5</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
         <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I4">
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="3"/>
         <v>44.523809523809526</v>
       </c>
       <c r="L4">
@@ -671,38 +641,36 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5" t="str">
         <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I5">
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J5" t="str">
-        <f t="shared" si="2"/>
-        <v>RED</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="3"/>
-        <v>-500</v>
+        <v>46.75</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -710,38 +678,36 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6">
-        <v>11.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H6">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I6">
+        <v>500</v>
+      </c>
+      <c r="J6" t="str">
         <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I6">
+        <v>GREEN</v>
+      </c>
+      <c r="K6">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="3"/>
-        <v>44.523809523809526</v>
+        <v>64.930555555555557</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -752,37 +718,35 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
         <v>29</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
       </c>
       <c r="G7">
         <v>10.5</v>
       </c>
       <c r="H7">
+        <v>10.5</v>
+      </c>
+      <c r="I7">
+        <v>500</v>
+      </c>
+      <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="I7">
+        <v>GREEN</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="3"/>
         <v>49.210526315789473</v>
       </c>
       <c r="L7">
@@ -794,38 +758,36 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
+        <v>500</v>
+      </c>
+      <c r="J8" t="str">
         <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I8">
+        <v>GREEN</v>
+      </c>
+      <c r="K8">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="3"/>
-        <v>44.523809523809526</v>
+        <v>58.4375</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -836,124 +798,38 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G9">
-        <v>8.1999999999999993</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H9">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="I9">
+        <v>500</v>
+      </c>
+      <c r="J9" t="str">
         <f t="shared" si="0"/>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="I9">
+        <v>GREEN</v>
+      </c>
+      <c r="K9">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J9" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="3"/>
-        <v>64.930555555555557</v>
+        <v>57.01219512195123</v>
       </c>
       <c r="L9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10">
-        <v>10.5</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J10" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="3"/>
-        <v>49.210526315789473</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11">
-        <v>9</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J11" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="3"/>
-        <v>58.4375</v>
-      </c>
-      <c r="L11">
         <v>1</v>
       </c>
     </row>
